--- a/projects/bms-room-allocation/SSC_BMS_room_findings.xlsx
+++ b/projects/bms-room-allocation/SSC_BMS_room_findings.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="SSC BMS allocation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Still to do" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Basement plant" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Still to do" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC BMS allocation'!$A$1:$J$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC BMS allocation'!$A$1:$J$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -507,31 +508,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1327</v>
+        <v>1318</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FCU0005</t>
+          <t>AHUB_0001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FCU-0005</t>
+          <t>AHU-B-0001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01.027 IDF-1</t>
+          <t>B.013 CHILLED WATER</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IDF-1 1.027</t>
+          <t>CHILLED WATER B.013</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IDF-1 1.027</t>
+          <t>CHILLED WATER B.013</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,7 +542,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FF-part2</t>
+          <t>BF-part1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -552,31 +553,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1329</v>
+        <v>1319</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FCU0007</t>
+          <t>AHUB_0002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FCU-0007</t>
+          <t>AHU-B-0002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>01.039 IDF-2</t>
+          <t>B.014 VENT PLANT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IDF-2 1.039</t>
+          <t>VENT PLANT B.014</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IDF-2 1.039</t>
+          <t>VENT PLANT B.014</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -586,7 +587,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FF-part2</t>
+          <t>BF-part1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -596,50 +597,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1332</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>FCU0010</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>FCU-0010</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>01.013 CORRIDOR</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDOR 1.010</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>AIR LOCK 1.011</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>AIR LOCK 1.011</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>FF-part1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="A4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AHUB_0003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AHU-B-0003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>B.014 VENT PLANT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VENT PLANT B.014</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VENT PLANT B.014</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -647,36 +643,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VAV0002</t>
+          <t>AHUB_0004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VAV-0002</t>
+          <t>AHU-B-0004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01.014 SHELL SPACE</t>
+          <t>B.008 VENT PLANT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.014</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SHELL SPACE NW 01.014</t>
+          <t>VENT PLANT B.008</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SHELL SPACE NW 01.014</t>
+          <t>VENT PLANT B.008</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -686,7 +677,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FF-part1</t>
+          <t>BF-part2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -696,45 +687,46 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>1336</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>VAV0003</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VAV-0003</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>01.014 SHELL SPACE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SHARED OFFICE 01.014</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SHARED OFFICE 01.014</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>FF-part1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>1322</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AHUB_0005</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>AHU-B-0005</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>B.014 VENT PLANT</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>CHILLED WATER B.013</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CHILLED WATER B.013</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -742,31 +734,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VAV0004</t>
+          <t>FCU0001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VAV-0004</t>
+          <t>FCU-0001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01.014 SHELL SPACE</t>
+          <t>B.016 SPRINKLER AND WATER</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.014</t>
+          <t>SPRINKLER AND WATER B.016</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SPRINKLER &amp; WATER RM B.016</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.014</t>
+          <t>SPRINKLER &amp; WATER RM B.016</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -776,7 +773,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FF-part1</t>
+          <t>BF-part1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -787,36 +784,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1338</v>
+        <v>1324</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VAV0005</t>
+          <t>FCU0002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VAV-0005</t>
+          <t>FCU-0002</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>01.015 SHELL SPACE</t>
+          <t>B.025 MAIN SEC CONTROL ROOM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.015</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SHELL SPACE SW 01.015</t>
+          <t>MAIN SEC. CONTROL ROOM B.025</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SHELL SPACE SW 01.015</t>
+          <t>MAIN SEC. CONTROL ROOM B.025</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -826,7 +818,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FF-part1</t>
+          <t>BF-part1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -836,77 +828,82 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1339</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VAV0006</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>VAV-0006</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>01.015 SHELL SPACE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SHARED OFFICE 01.015</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SHARED OFFICE 01.015</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>FF-part1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="A9" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FCU0003</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>FCU-0003</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>B.030 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>B.M.S B.039</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>BMS B.039</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>BMS B.039</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>check</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VAV0007</t>
+          <t>FCU0005</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VAV-0007</t>
+          <t>FCU-0005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01.015 SHELL SPACE</t>
+          <t>01.027 IDF-1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.015</t>
+          <t>IDF-1 1.027</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.015</t>
+          <t>IDF-1 1.027</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -916,7 +913,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FF-part1</t>
+          <t>FF-part2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -927,36 +924,31 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1341</v>
+        <v>1329</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VAV0008</t>
+          <t>FCU0007</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VAV-0008</t>
+          <t>FCU-0007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>01.024 CORRIDOR</t>
+          <t>01.039 IDF-2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CORRIDOR 01.024</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CORRIDORS SE 01.024</t>
+          <t>IDF-2 1.039</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORRIDORS SE 01.024</t>
+          <t>IDF-2 1.039</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -977,32 +969,36 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1342</v>
+        <v>1332</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VAV0009</t>
+          <t>FCU0010</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VAV-0009</t>
+          <t>FCU-0010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>01.002 SHELL SPACE</t>
+          <t>01.013 CORRIDOR</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n"/>
+          <t>CORRIDOR 1.010</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>AIR LOCK 1.011</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
+          <t>AIR LOCK 1.011</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1023,31 +1019,31 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1343</v>
+        <v>1334</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VAV0010</t>
+          <t>VAV0001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VAV-0010</t>
+          <t>VAV-0001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>01.019 PRAYER ROOM</t>
+          <t>B.015 ENTRANCE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
+          <t>ENTRANCE B.015</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
+          <t>ENTRANCE B.015</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1057,7 +1053,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FF-part1</t>
+          <t>BF-part1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1068,31 +1064,36 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1345</v>
+        <v>1335</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VAV0012</t>
+          <t>VAV0002</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VAV-0012</t>
+          <t>VAV-0002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>01.019 PRAYER ROOM</t>
+          <t>01.014 SHELL SPACE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
+          <t>SHARED OFFICE 01.014</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SHELL SPACE NW 01.014</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
+          <t>SHELL SPACE NW 01.014</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1113,31 +1114,31 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1346</v>
+        <v>1336</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VAV0013</t>
+          <t>VAV0003</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VAV-0013</t>
+          <t>VAV-0003</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01.019 PRAYER ROOM</t>
+          <t>01.014 SHELL SPACE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
+          <t>SHARED OFFICE 01.014</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PRAYER ROOM 01.019</t>
+          <t>SHARED OFFICE 01.014</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1148,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FF-part2</t>
+          <t>FF-part1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1157,83 +1158,82 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>1347</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>VAV0014</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>VAV-0014</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>01.019 PRAYER ROOM</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>PRAYER ROOM 01.019</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>PRAYER ROOM 01.019</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>FF-part2</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="A16" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VAV0004</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VAV-0004</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>01.014 SHELL SPACE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SHARED OFFICE 01.014</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SHARED OFFICE 01.014</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FF-part1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1348</v>
+        <v>1338</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VAV0015</t>
+          <t>VAV0005</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VAV-0015</t>
+          <t>VAV-0005</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>01.029 SHELL SPACE</t>
+          <t>01.015 SHELL SPACE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROOM NO 42</t>
+          <t>SHARED OFFICE 01.015</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SHELL SPACE E 01.029</t>
+          <t>SHELL SPACE SW 01.015</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SHELL SPACE E 01.029</t>
+          <t>SHELL SPACE SW 01.015</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FF-part2</t>
+          <t>FF-part1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1254,41 +1254,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1349</v>
+        <v>1339</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VAV0016</t>
+          <t>VAV0006</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VAV-0016</t>
+          <t>VAV-0006</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01.029 SHELL SPACE</t>
+          <t>01.015 SHELL SPACE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ROOM NO 43</t>
+          <t>SHARED OFFICE 01.015</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ROOM NO 43</t>
+          <t>SHARED OFFICE 01.015</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>could not compare room numbers</t>
+          <t>confirms the register</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FF-part2</t>
+          <t>FF-part1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1299,41 +1299,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1350</v>
+        <v>1340</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VAV0017</t>
+          <t>VAV0007</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VAV-0017</t>
+          <t>VAV-0007</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01.029 SHELL SPACE</t>
+          <t>01.015 SHELL SPACE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ROOM NO 44</t>
+          <t>SHARED OFFICE 01.015</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ROOM NO 44</t>
+          <t>SHARED OFFICE 01.015</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>could not compare room numbers</t>
+          <t>confirms the register</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FF-part2</t>
+          <t>FF-part1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1344,31 +1344,36 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1351</v>
+        <v>1341</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VAV0018</t>
+          <t>VAV0008</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VAV-0018</t>
+          <t>VAV-0008</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01.029 SHELL SPACE</t>
+          <t>01.024 CORRIDOR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.029</t>
+          <t>CORRIDOR 01.024</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CORRIDORS SE 01.024</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SHARED OFFICE 01.029</t>
+          <t>CORRIDORS SE 01.024</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1388,45 +1393,46 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>1352</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>VAV0019</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>VAV-0019</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>01.029 SHELL SPACE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SHARED OFFICE 01.029</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SHARED OFFICE 01.029</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>FF-part2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="A21" s="2" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>VAV0009</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0009</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>01.002 SHELL SPACE</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>PRAYER ROOM 01.019</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>PRAYER ROOM 01.019</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>FF-part1</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -1434,36 +1440,31 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1354</v>
+        <v>1343</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VAV0021</t>
+          <t>VAV0010</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VAV-0021</t>
+          <t>VAV-0010</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>01.013 CORRIDOR</t>
+          <t>01.019 PRAYER ROOM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CORRIDOR 01.013</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CORRIDORS W 01.013</t>
+          <t>PRAYER ROOM 01.019</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORRIDORS W 01.013</t>
+          <t>PRAYER ROOM 01.019</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1483,50 +1484,45 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>1357</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>VAV0024</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0024</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>01.003 OPEN SPACE</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDOR 01.001</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDORS S 01.001</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDORS S 01.001</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="A23" t="n">
+        <v>1345</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VAV0012</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VAV-0012</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>01.019 PRAYER ROOM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PRAYER ROOM 01.019</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PRAYER ROOM 01.019</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>FF-part1</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -1534,31 +1530,31 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1358</v>
+        <v>1346</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VAV0025</t>
+          <t>VAV0013</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VAV-0025</t>
+          <t>VAV-0013</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01.002 SHELL SPACE</t>
+          <t>01.019 PRAYER ROOM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TEAM SPACE 01.002</t>
+          <t>PRAYER ROOM 01.019</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TEAM SPACE 01.002</t>
+          <t>PRAYER ROOM 01.019</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1568,7 +1564,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FF-part1</t>
+          <t>FF-part2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1578,141 +1574,141 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>1360</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>VAV0027</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>VAV-0027</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>01.002 SHELL SPACE</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>TEAM SPACE 01.002</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>TEAM SPACE 01.002</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="A25" s="3" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>VAV0014</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>VAV-0014</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>01.019 PRAYER ROOM</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>PRAYER ROOM 01.019</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>PRAYER ROOM 01.019</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>1361</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>VAV0028</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0028</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>01.002 SHELL SPACE</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>TEAM SPACE 01.002</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>OPEN OFFICE BELOW SKYLIGHT 01.003</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>OPEN OFFICE BELOW SKYLIGHT 01.003</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="A26" t="n">
+        <v>1348</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VAV0015</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VAV-0015</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>01.029 SHELL SPACE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ROOM NO 42</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SHELL SPACE E 01.029</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SHELL SPACE E 01.029</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>1362</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>VAV0029</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0029</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>01.003 OPEN SPACE</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDOR 01.001</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDOR 01.001</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="A27" t="n">
+        <v>1349</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VAV0016</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VAV-0016</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>01.029 SHELL SPACE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ROOM NO 43</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ROOM NO 43</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>could not compare room numbers</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -1720,46 +1716,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1363</v>
+        <v>1350</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VAV0030</t>
+          <t>VAV0017</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VAV-0030</t>
+          <t>VAV-0017</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>01.016 SHELL SPACE</t>
+          <t>01.029 SHELL SPACE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PRINT COPY 01.016</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>PRINTING ROOM SHELL SPACE 01.016</t>
+          <t>ROOM NO 44</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PRINTING ROOM SHELL SPACE 01.016</t>
+          <t>ROOM NO 44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>confirms the register</t>
+          <t>could not compare room numbers</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FF-part1</t>
+          <t>FF-part2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1769,46 +1760,45 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>1364</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>VAV0031</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0031</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>01.003 OPEN SPACE</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDOR 01.001</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDOR 01.001</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>FF-part1</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="A29" t="n">
+        <v>1351</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VAV0018</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VAV-0018</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>01.029 SHELL SPACE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SHARED OFFICE 01.029</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SHARED OFFICE 01.029</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -1816,36 +1806,31 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1365</v>
+        <v>1352</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VAV0032</t>
+          <t>VAV0019</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VAV-0032</t>
+          <t>VAV-0019</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>01.018 CORRIDOR</t>
+          <t>01.029 SHELL SPACE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CORRIDOR 01.018</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>CORRIDORS SW 01.018</t>
+          <t>SHARED OFFICE 01.029</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORRIDORS SW 01.018</t>
+          <t>SHARED OFFICE 01.029</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1855,60 +1840,60 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1354</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>VAV0021</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VAV-0021</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>01.013 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.013</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CORRIDORS W 01.013</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CORRIDORS W 01.013</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>FF-part1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>1366</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>VAV0033</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0033</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>01.025 MALE TOILET</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDOR 01.028</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>IDF 01.027 &amp; 39</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>IDF 01.027 &amp; 39</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>FF-part2</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -1916,16 +1901,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>VAV0034</t>
+          <t>VAV0024</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VAV-0034</t>
+          <t>VAV-0024</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1935,17 +1920,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>OPEN SPACE 01.003</t>
+          <t>CORRIDOR 01.001</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>CORRIDOR CENTRAL 01.004</t>
+          <t>CORRIDORS S 01.001</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>CORRIDOR CENTRAL 01.004</t>
+          <t>CORRIDORS S 01.001</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1966,36 +1951,31 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1368</v>
+        <v>1358</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VAV0035</t>
+          <t>VAV0025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VAV-0035</t>
+          <t>VAV-0025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>01.028 CORRIDOR</t>
+          <t>01.002 SHELL SPACE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CORRIDOR 01.010</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CORRIDORS E 01.028</t>
+          <t>TEAM SPACE 01.002</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORRIDORS E 01.028</t>
+          <t>TEAM SPACE 01.002</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2005,60 +1985,55 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>FF-part1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1360</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>VAV0027</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VAV-0027</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>01.002 SHELL SPACE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>TEAM SPACE 01.002</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>TEAM SPACE 01.002</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>1369</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>VAV0036</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0036</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>01.019 PRAYER ROOM</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>ABLUTION ROOM 01.022</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>ABLUTION ROOMS 01.020 &amp; 23</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>ABLUTION ROOMS 01.020 &amp; 23</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>FF-part2</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -2066,36 +2041,36 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1372</v>
+        <v>1361</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VAV0039</t>
+          <t>VAV0028</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VAV-0039</t>
+          <t>VAV-0028</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>01.028 CORRIDOR</t>
+          <t>01.002 SHELL SPACE</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>OPEN SPACE 01.003</t>
+          <t>TEAM SPACE 01.002</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>CORRIDOR AUDITORIUM E 01.035</t>
+          <t>OPEN OFFICE BELOW SKYLIGHT 01.003</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>CORRIDOR AUDITORIUM E 01.035</t>
+          <t>OPEN OFFICE BELOW SKYLIGHT 01.003</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2110,50 +2085,51 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>check</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>1373</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>VAV0040</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>VAV-0040</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>02.006 CONFERENCE ROOM</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CONFERENCE ROOM 02.006</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>CONFERENCE ROOM 02.006</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Second Floor</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="A36" s="2" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>VAV0029</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0029</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>01.003 OPEN SPACE</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.001</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.001</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -2161,31 +2137,36 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1374</v>
+        <v>1363</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VAV0041</t>
+          <t>VAV0030</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VAV-0041</t>
+          <t>VAV-0030</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02.005 EXECUTIVE CONFERENCE ROOM</t>
+          <t>01.016 SHELL SPACE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
+          <t>PRINT COPY 01.016</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PRINTING ROOM SHELL SPACE 01.016</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
+          <t>PRINTING ROOM SHELL SPACE 01.016</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2195,7 +2176,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Second Floor</t>
+          <t>FF-part1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2205,228 +2186,246 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>1375</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>VAV0042</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>VAV-0042</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>02.005 EXECUTIVE CONFERENCE ROOM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Second Floor</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="A38" s="2" t="n">
+        <v>1364</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>VAV0031</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0031</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>01.003 OPEN SPACE</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.001</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.001</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>FF-part1</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>1379</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>VAV0046</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>VAV-0046</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>02.002 LOBBY</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Second Floor</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="A39" t="n">
+        <v>1365</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VAV0032</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VAV-0032</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>01.018 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.018</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CORRIDORS SW 01.018</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CORRIDORS SW 01.018</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>FF-part1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>1380</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>VAV0047</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>VAV-0047</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>02.002 LOBBY</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>Second Floor</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>check</t>
+      <c r="A40" s="2" t="n">
+        <v>1366</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>VAV0033</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0033</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>01.025 MALE TOILET</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.028</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>IDF 01.027 &amp; 39</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>IDF 01.027 &amp; 39</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>1381</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>VAV0048</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>VAV-0048</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>02.002 LOBBY</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Second Floor</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="A41" s="2" t="n">
+        <v>1367</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>VAV0034</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0034</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>01.003 OPEN SPACE</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>OPEN SPACE 01.003</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR CENTRAL 01.004</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR CENTRAL 01.004</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>FF-part1</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>1382</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>VAV0049</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0049</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>02.003 CORRIDOR</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>LOBBY 02.002</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Second Floor</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="A42" t="n">
+        <v>1368</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>VAV0035</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VAV-0035</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>01.028 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CORRIDOR 01.010</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CORRIDORS E 01.028</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CORRIDORS E 01.028</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -2434,32 +2433,36 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1383</v>
+        <v>1369</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>VAV0050</t>
+          <t>VAV0036</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VAV-0050</t>
+          <t>VAV-0036</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>02.002 LOBBY</t>
+          <t>01.019 PRAYER ROOM</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CORRIDOR 02.003</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n"/>
+          <t>ABLUTION ROOM 01.022</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>ABLUTION ROOMS 01.020 &amp; 23</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>CORRIDOR 02.003</t>
+          <t>ABLUTION ROOMS 01.020 &amp; 23</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2469,56 +2472,60 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Second Floor</t>
+          <t>FF-part2</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>check</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>1384</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>VAV0051</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>VAV-0051</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>02.005 EXECUTIVE CONFERENCE ROOM</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>Second Floor</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="n">
+        <v>1372</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>VAV0039</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0039</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>01.028 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>OPEN SPACE 01.003</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR AUDITORIUM E 01.035</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR AUDITORIUM E 01.035</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>check</t>
         </is>
@@ -2526,16 +2533,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1385</v>
+        <v>1373</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VAV0052</t>
+          <t>VAV0040</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VAV-0052</t>
+          <t>VAV-0040</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2571,31 +2578,31 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1386</v>
+        <v>1374</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VAV0053</t>
+          <t>VAV0041</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VAV-0053</t>
+          <t>VAV-0041</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>03.015 RESEARCHER OFFICE</t>
+          <t>02.005 EXECUTIVE CONFERENCE ROOM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.015</t>
+          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.015</t>
+          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2605,7 +2612,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>Second Floor</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2616,31 +2623,31 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VAV0054</t>
+          <t>VAV0042</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VAV-0054</t>
+          <t>VAV-0042</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>03.014 VISITORS CUBIDE</t>
+          <t>02.005 EXECUTIVE CONFERENCE ROOM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.014</t>
+          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.014</t>
+          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2650,7 +2657,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>Second Floor</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2660,122 +2667,124 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>1388</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>VAV0055</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>VAV-0055</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>03.013 RESEARCHER OFFICE</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.013</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.013</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="A48" s="3" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>VAV0046</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>VAV-0046</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>02.002 LOBBY</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>LOBBY 02.002</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>LOBBY 02.002</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Second Floor</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>1389</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>VAV0056</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>VAV-0056</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>03.012 RESEARCHER OFFICE</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.012</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.012</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="A49" s="3" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>VAV0047</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>VAV-0047</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>02.002 LOBBY</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>LOBBY 02.002</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>LOBBY 02.002</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Second Floor</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1390</v>
+        <v>1381</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VAV0057</t>
+          <t>VAV0048</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VAV-0057</t>
+          <t>VAV-0048</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>03.011 VISITORS CUBIDE</t>
+          <t>02.002 LOBBY</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.011</t>
+          <t>LOBBY 02.002</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.011</t>
+          <t>LOBBY 02.002</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2785,7 +2794,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>Second Floor</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2795,168 +2804,170 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>1391</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>VAV0058</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>VAV-0058</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>03.010 RESEARCHER OFFICE</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.010</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.010</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="A51" s="2" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>VAV0049</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0049</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>02.003 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>LOBBY 02.002</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>LOBBY 02.002</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Second Floor</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>1392</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>VAV0059</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>VAV-0059</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>03.009 RESEARCHER OFFICE</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.009</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.009</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>VAV0050</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0050</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>02.002 LOBBY</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR 02.003</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR 02.003</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Second Floor</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>1393</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>VAV0060</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>VAV-0060</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>03.008 VISITORS CUBIDE</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>VISITOR'S CUBICLE 03.008</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>VISITOR'S CUBICLE 03.008</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="A53" s="3" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>VAV0051</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>VAV-0051</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>02.005 EXECUTIVE CONFERENCE ROOM</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>EXECUTIVE CONFERENCE ROOM 02.005</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Second Floor</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1394</v>
+        <v>1385</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VAV0061</t>
+          <t>VAV0052</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VAV-0061</t>
+          <t>VAV-0052</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>03.007 OPERATIONS MANAGERS</t>
+          <t>02.006 CONFERENCE ROOM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OPERATION MANAGERS 03.007</t>
+          <t>CONFERENCE ROOM 02.006</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>OPERATION MANAGERS 03.007</t>
+          <t>CONFERENCE ROOM 02.006</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2966,363 +2977,358 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t>Second Floor</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VAV0053</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VAV-0053</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>03.015 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.015</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.015</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>TF-part1</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>1395</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>VAV0062</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0062</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>03.006A ROOM</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>ROOM 03.006B</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>ROOM 03.006B</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>TF-part2</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>1404</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>VAV0071</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0071</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>03.032 GENERAL OFFICE AREA</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>TF-part2</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="A56" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>VAV0054</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VAV-0054</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>03.014 VISITORS CUBIDE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.014</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.014</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>1405</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>VAV0072</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0072</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>03.032 GENERAL OFFICE AREA</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>TF-part2</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="A57" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>VAV0055</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VAV-0055</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>03.013 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.013</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.013</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>1408</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>VAV0075</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0075</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>03.032 GENERAL OFFICE AREA</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>TF-part2</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="A58" t="n">
+        <v>1389</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>VAV0056</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VAV-0056</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>03.012 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.012</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.012</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>1410</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>VAV0077</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>VAV-0077</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>03.032 GENERAL OFFICE AREA</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>ROOM NUMBER DIFFERS</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>TF-part2</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="A59" t="n">
+        <v>1390</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>VAV0057</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VAV-0057</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>03.011 VISITORS CUBIDE</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.011</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.011</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>1411</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>VAV0078</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>VAV-0078</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>03.031 ASSOC.DIR OFFICE</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ASSOC. DOR. OFFICE 03.031</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>ASSOC. DOR. OFFICE 03.031</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>TF-part2</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="A60" t="n">
+        <v>1391</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>VAV0058</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VAV-0058</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>03.010 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.010</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.010</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>1392</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>VAV0059</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>VAV-0059</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>03.009 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.009</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.009</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>check</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>1413</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>VAV0080</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>VAV-0080</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>03.030 ASSOC.DIR MEETING ROOM</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ASSOC. DIR. MEETING ROOM 03.030</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>ASSOC. DIR. MEETING ROOM 03.030</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>TF-part2</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1414</v>
+        <v>1393</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VAV0081</t>
+          <t>VAV0060</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VAV-0081</t>
+          <t>VAV-0060</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>03.029 RESEARCHER OFFICE</t>
+          <t>03.008 VISITORS CUBIDE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.029</t>
+          <t>VISITOR'S CUBICLE 03.008</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.029</t>
+          <t>VISITOR'S CUBICLE 03.008</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3332,7 +3338,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TF-part2</t>
+          <t>TF-part1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3343,31 +3349,31 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1415</v>
+        <v>1394</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VAV0082</t>
+          <t>VAV0061</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VAV-0082</t>
+          <t>VAV-0061</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>03.028 VISITORS CUBIDE</t>
+          <t>03.007 OPERATIONS MANAGERS</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.028</t>
+          <t>OPERATION MANAGERS 03.007</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.028</t>
+          <t>OPERATION MANAGERS 03.007</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3377,312 +3383,318 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>1395</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>VAV0062</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0062</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>03.006A ROOM</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>ROOM 03.006B</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>ROOM 03.006B</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
           <t>TF-part2</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>1416</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>VAV0083</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>VAV-0083</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>03.027 RESEARCHER OFFICE</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.027</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.027</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>VAV0071</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0071</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>03.032 GENERAL OFFICE AREA</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>TF-part2</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>1418</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>VAV0085</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>VAV-0085</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>03.026 MEETING ROOM</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>MEETING ROOM 03.026</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>MEETING ROOM 03.026</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>VAV0072</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0072</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>03.032 GENERAL OFFICE AREA</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>TF-part2</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>1419</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>VAV0086</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>VAV-0086</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>03.026 MEETING ROOM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>MEETING ROOM 03.026</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>MEETING ROOM 03.026</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>VAV0075</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0075</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>03.032 GENERAL OFFICE AREA</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>TF-part2</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>1420</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>VAV0087</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>VAV-0087</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>03.025 SECRETARIAL AREA</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>SECRETARIAL AREA 03.025</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>SECRETARIAL AREA 03.025</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>1421</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>VAV0088</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>VAV-0088</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>03.024 VISITORS CUBIDE</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>VISITOR'S CUBICLE 03.024</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>VISITOR'S CUBICLE 03.024</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="A68" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>VAV0077</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>VAV-0077</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>03.032 GENERAL OFFICE AREA</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>ROOM NUMBER DIFFERS</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>TF-part2</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>1422</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>VAV0089</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>VAV-0089</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>03.023 RESEARCHER OFFICE</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.023</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>RESEARCHER OFFICE 03.023</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>TF-part1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="A69" s="3" t="n">
+        <v>1411</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>VAV0078</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>VAV-0078</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>03.031 ASSOC.DIR OFFICE</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>ASSOC. DOR. OFFICE 03.031</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>ASSOC. DOR. OFFICE 03.031</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>TF-part2</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1423</v>
+        <v>1413</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VAV0090</t>
+          <t>VAV0080</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VAV-0090</t>
+          <t>VAV-0080</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>03.022 RESEARCHER OFFICE</t>
+          <t>03.030 ASSOC.DIR MEETING ROOM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.022</t>
+          <t>ASSOC. DIR. MEETING ROOM 03.030</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.022</t>
+          <t>ASSOC. DIR. MEETING ROOM 03.030</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3692,7 +3704,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>TF-part2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3703,31 +3715,31 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1424</v>
+        <v>1414</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VAV0091</t>
+          <t>VAV0081</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VAV-0091</t>
+          <t>VAV-0081</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>03.021 VISITORS CUBIDE</t>
+          <t>03.029 RESEARCHER OFFICE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.021</t>
+          <t>RESEARCHER OFFICE 03.029</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.021</t>
+          <t>RESEARCHER OFFICE 03.029</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3737,7 +3749,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>TF-part2</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3748,31 +3760,31 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1425</v>
+        <v>1415</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VAV0092</t>
+          <t>VAV0082</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VAV-0092</t>
+          <t>VAV-0082</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>03.020 RESEARCHER OFFICE</t>
+          <t>03.028 VISITORS CUBIDE</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.020</t>
+          <t>VISITOR'S CUBICLE 03.028</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.020</t>
+          <t>VISITOR'S CUBICLE 03.028</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3782,7 +3794,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>TF-part2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3793,31 +3805,31 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VAV0093</t>
+          <t>VAV0083</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VAV-0093</t>
+          <t>VAV-0083</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>03.019 IT MANAGERS OFFICE</t>
+          <t>03.027 RESEARCHER OFFICE</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IT MANAGERS'S OFFICE 03.019</t>
+          <t>RESEARCHER OFFICE 03.027</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>IT MANAGERS'S OFFICE 03.019</t>
+          <t>RESEARCHER OFFICE 03.027</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3827,7 +3839,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>TF-part2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3838,31 +3850,31 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1427</v>
+        <v>1418</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VAV0094</t>
+          <t>VAV0085</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VAV-0094</t>
+          <t>VAV-0085</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>03.018 VISITORS CUBIDE</t>
+          <t>03.026 MEETING ROOM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.018</t>
+          <t>MEETING ROOM 03.026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>VISITOR'S CUBICLE 03.018</t>
+          <t>MEETING ROOM 03.026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3872,7 +3884,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>TF-part2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3883,31 +3895,31 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1428</v>
+        <v>1419</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VAV0095</t>
+          <t>VAV0086</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VAV-0095</t>
+          <t>VAV-0086</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>03.017 RESEARCHER OFFICE</t>
+          <t>03.026 MEETING ROOM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.017</t>
+          <t>MEETING ROOM 03.026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>RESEARCHER OFFICE 03.017</t>
+          <t>MEETING ROOM 03.026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3917,7 +3929,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TF-part1</t>
+          <t>TF-part2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3928,36 +3940,31 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1440</v>
+        <v>1420</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VAV0107</t>
+          <t>VAV0087</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VAV-0107</t>
+          <t>VAV-0087</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>03.032 GENERAL OFFICE AREA</t>
+          <t>03.025 SECRETARIAL AREA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GENERAL OFFICE AREA 03.002</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>GENERAL OFFICE AREA 03.032</t>
+          <t>SECRETARIAL AREA 03.025</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>GENERAL OFFICE AREA 03.032</t>
+          <t>SECRETARIAL AREA 03.025</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3967,7 +3974,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TF-part2</t>
+          <t>TF-part1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3978,125 +3985,995 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
+        <v>1421</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>VAV0088</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VAV-0088</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>03.024 VISITORS CUBIDE</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.024</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.024</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1422</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>VAV0089</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VAV-0089</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>03.023 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.023</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.023</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>VAV0090</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VAV-0090</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>03.022 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.022</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.022</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1424</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>VAV0091</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VAV-0091</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>03.021 VISITORS CUBIDE</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.021</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.021</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VAV0092</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VAV-0092</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>03.020 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.020</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.020</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1426</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VAV0093</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>VAV-0093</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>03.019 IT MANAGERS OFFICE</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>IT MANAGERS'S OFFICE 03.019</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>IT MANAGERS'S OFFICE 03.019</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>VAV0094</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VAV-0094</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>03.018 VISITORS CUBIDE</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.018</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>VISITOR'S CUBICLE 03.018</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1428</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VAV0095</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VAV-0095</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>03.017 RESEARCHER OFFICE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.017</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>RESEARCHER OFFICE 03.017</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TF-part1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VAV0107</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VAV-0107</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>03.032 GENERAL OFFICE AREA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.002</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.032</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>GENERAL OFFICE AREA 03.032</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TF-part2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
         <v>1441</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>VAV0108</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>VAV-0108</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>03.032 GENERAL OFFICE AREA</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>GENERAL OFFICE AREA 03.002</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>GENERAL OFFICE AREA 03.032</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>GENERAL OFFICE AREA 03.032</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>confirms the register</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>confirms the register</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>TF-part2</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
         <is>
           <t>KEF0103</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>KEF-1F-0103</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>01.005 KITCHEN</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>not in the SSC controllable register</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
         <is>
           <t>TEF0101</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>TEF-1F-0101</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>01.028 CORRIDOR</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>not in the SSC controllable register</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>FF-part2</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J79"/>
+  <autoFilter ref="A1:J88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BMS tag</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Room per BMS</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Read confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CCU-B-005B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B.023 Q TEL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CCU-B-006B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B.023 Q TEL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>CCU-B-006A</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>B.023 Q TEL</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CCU-B-0007</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B.026 MDF/SER.1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CCU-B-0004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B.017 MDF-2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CCU-B-002A</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>B.038 SER-2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>CCU-B-001B</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>B.038 SER-2</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>CCU-B-002B</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>B.038 SER-2</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>DX-B-0001</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>B.022 SSP</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DX-B-0002</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>B.022 SSP</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>BF-part1</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DX-B-0003</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B.005 UPS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BF-part2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DX-B-0004</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>B.008 VENT PLANT</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>BF-part2</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DX-B-0006</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B.001 FM STORAGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BF-part2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DX-B-0007</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B.006 SERVICE AREA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BF-part2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DX-B-0008</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B.008 VENT PLANT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BF-part2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DX-B-0009</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B.002 HV ROOM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BF-part2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>DX-B-0010</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>B.033 CLOSET</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>BF-part2</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KEF-1F-0103</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>01.005 KITCHEN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TEF-1F-0101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>01.028 CORRIDOR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FF-part2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4129,7 +5006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AHU-B-0001/0002/0003/0005, CCU-B-001A/001B/002A/002B/0003/0004/005A/005B/006A/006B/0007/0008, DX-B-0001/0002, FCU-0001/0002/0003, VAV-0001</t>
+          <t>CCU-B-001A, CCU-B-0003, CCU-B-0008, CCU-B-005A - leaders share a path with their neighbours and cannot be told apart at this resolution</t>
         </is>
       </c>
     </row>
@@ -4141,7 +5018,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AHU-B-0004, DX-B-0003..0010, GEF-B-0001</t>
+          <t>DX-B-0005, GEF-B-0001</t>
         </is>
       </c>
     </row>
